--- a/Util/standardList.xlsx
+++ b/Util/standardList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\competition\seasideProgram\StraitsCup\Util\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633C20D2-7096-4753-942D-34DAE7E98324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADED9C5-7753-4B8F-A97A-112474F5605D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>项目名称</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -48,39 +48,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>南音</t>
-  </si>
-  <si>
-    <t>联合国人类非物质文化遗产代表作、国家级</t>
-  </si>
-  <si>
-    <t>传统音乐</t>
-  </si>
-  <si>
-    <t>泉州市、厦门市</t>
-  </si>
-  <si>
-    <t>南音又称“弦管”，是中国现存最古老的乐种之一，起源于唐，形成于宋，保留了古代乐器形制与记谱法，被誉为“中国音乐史上的活化石”。其演唱使用泉州方言，曲调典雅，体系完整。</t>
-  </si>
-  <si>
-    <t>《陈三五娘》《八骏马》《梅花操》</t>
-  </si>
-  <si>
-    <t>妈祖信俗</t>
-  </si>
-  <si>
-    <t>民俗</t>
-  </si>
-  <si>
-    <t>莆田市湄洲岛、泉州市、福州市</t>
-  </si>
-  <si>
-    <t>妈祖信俗是以妈祖（林默）崇拜为核心的民间信仰体系，起源于宋代福建莆田湄洲岛。信众遍布全球46个国家，有上万座妈祖庙。每年农历三月廿三妈祖诞辰举行盛大祭典，体现海洋文化与华人社群凝聚力。</t>
-  </si>
-  <si>
-    <t>湄洲祖庙祭典、妈祖巡安、海祭仪式</t>
-  </si>
-  <si>
     <t>泉州提线木偶戏</t>
   </si>
   <si>
@@ -127,13 +94,1195 @@
   </si>
   <si>
     <t>大红袍、肉桂、水仙</t>
+  </si>
+  <si>
+    <t>福州软木画</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>福州市</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>福州软木画，又称软木雕或木画，是中国传统民间雕刻工艺品之一，主要产于福建省福州市。它是一种“雕”与“画”相结合的独特手工艺，以精细的刻工、纯朴的色调和逼真的形象著称，尤其擅长表现中国古代的亭台楼阁、园林景色，观者常有身临其境之感。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>软木画所用的主要原料是从西班牙、葡萄牙等地进口的栓皮栎树的软木，这种材料质地轻软、富有弹性，非常适合进行精细雕刻。匠人们运用浮雕、圆雕、透雕等多种传统雕刻技法，将软木切成薄片后，手工刻出花草、树木、楼阁、人物、桥梁、船只等微小部件，再用通草制作白鹤、孔雀、麋鹿等鸟兽形象，依据整体画面设计，将这些零件粘贴在衬纸上，构成立体或半立体的画面，最后装入玻璃框中，形成一件完整的艺术品。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>软木画起源于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1914</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年。当时福建巡按使许世英从德国带回一幅类似圣诞贺卡的风景画片，交由福州工艺传习所的雕刻师傅陈春润（外号“牛仔师”）研究仿制。陈春润与木雕艺人吴启棋、郑立溪等人发现该画片所用材料与软木相似，于是尝试用本地可得的软木进行仿制，最初仅用于制作简单的贺年片。到了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>世纪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年代，软木画开始向平面多层（半浮雕）形式发展，并借鉴宋代山水画的构图方式，逐渐演变为可悬挂于墙上的镜框式工艺品。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吴启棋（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1893</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>—</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1957</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）是福州软木画的重要创始人之一，原为木雕艺人，来自福州北郊西园村。在传习所停办后，他回到家乡带徒授艺，使西园村成为软木画的重要生产基地。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1931</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，他在福州城内开设“启棋木画店”，其弟及徒弟也陆续开设店铺，推动了软木画的商业化发展。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年代后期，受杭州西湖风景照片启发，吴启棋创作了大量以名胜风景为主题的软木画作品，其徒弟如陈康、魏良栋等也纷纷以各地园林为题材进行创作，并将产品销往港澳及东南亚地区，使福州软木画成功打入国际市场。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>新中国成立后，软木画产业进一步壮大。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1953</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，吴启棋家族中的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人组建了合作社，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1958</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年发展为福州木画厂，从业人员不断增多。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1956</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，吴启棋的高徒陈锟、陈庄等人创新性地采用圆雕与透雕技法，创作出立体软木画《天安门》，开创了软木画的新表现形式。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1957</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，吴启棋与陈锟的作品《天安门》《万寿山》《颐和园》参加首届全国工艺美术艺人代表大会展览，获得高度评价。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1959</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，福州木画厂创作的《福州西湖》《厦门鹭岛风光》《泉州东西塔》《武夷春色》等作品被选入人民大会堂福建厅陈列，标志着软木画艺术地位的提升。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>此后，福州木画厂不断拓展产品种类，从大型屏风、挂屏到实用型首饰盒、镜台等小型摆件，品种多达数百种。产品远销至港澳、东南亚、日本乃至欧美等几十个国家和地区，一度成为出口创汇最高的工艺品之一。软木画也因此与寿山石雕、脱胎漆器并称为“榕城三绝”，成为福州最具代表性的三大传统工艺。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2008</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，福州软木画被列入第二批国家级非物质文化遗产名录，正式获得国家层面的文化保护地位。近年来，为适应新时代审美与市场需求，软木画也在不断创新。例如，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2025</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年央视曾专题报道福州“将软木画戴在头上”的沉浸式体验活动，非遗传承人林清韵通过跨界合作，将软木画元素融入时尚配饰，使其以更年轻、更生活化的方式走进公众视野。这种“古艺进生活”的尝试，不仅提升了软木画的传播力，也为其传承注入了新活力。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>制作一幅软木画工序繁复，需经历选料、画稿、切片、雕刻、拼贴等多个环节，其中最精细的部件厚度可薄至几毫米，全靠匠人手工完成，耗时耗力，极具艺术价值与收藏价值。目前，福州仍有如“福州吴芝生软木画有限公司”等企业在坚持生产与推广这一传统工艺，同时也有非遗传承人致力于教学与创新，努力让这门百年技艺在当代焕发新生。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《天安门》是福州软木画历史上具有里程碑意义的作品。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1956</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，由吴启棋的高徒陈锟、陈庄等人首次采用圆雕与透雕技法创作出立体式软木画《天安门》，突破了传统平面或半浮雕形式的局限，开创了软木画立体表现的新路径。这件作品在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1957</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年首届全国工艺美术艺人代表大会上展出，获得高度评价，被视为软木画从民间工艺品迈向国家级艺术精品的重要标志。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《万寿山》和《颐和园》也是早期极具影响力的代表作，同样出自吴启棋及其弟子之手。这两幅作品以北京皇家园林为题材，通过多层镂空雕刻和精细拼贴，再现了亭台楼阁、回廊水榭、古树奇石等细节，层次分明、透视准确，充分展现了软木画“以小见大、咫尺千里”的艺术特色。它们与《天安门》一同被选送参加全国展览，并长期作为国家礼品赠予外宾。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《福州西湖》是体现地方特色的经典之作。该作品以福州本地著名景点西湖公园为蓝本，融合宋代山水画的构图理念，将湖心亭、柳堤、拱桥、游船等元素巧妙组合，既写实又富有诗意。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1959</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年，这幅作品与其他几件福建题材软木画（如《厦门鹭岛风光》《泉州东西塔》《武夷春色》）一同被选入人民大会堂福建厅陈列，成为展示福建文化的重要窗口。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《武夷春色》则以福建名山武夷山为题材，通过软木雕刻出九曲溪、玉女峰、大王峰等标志性景观，辅以通草制作的飞鸟、小舟和人物，营造出春意盎然、山水相依的意境。这类自然风景题材作品最能体现软木画“雕中有画、画中有景”的独特魅力。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>此外，在出口创汇时期，还有大量以苏州园林（如拙政园、留园）、杭州西湖、桂林山水等中国名胜为主题的软木画作品远销海外，成为国际社会了解中国传统美学的重要载体。其中一些精品至今仍收藏于海外博物馆或华人家庭中。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>近年来，新一代传承人也在创作具有时代气息的新代表作。例如，非遗传承人林清韵推出的《三坊七巷》系列软木画，将福州历史文化街区以微缩立体形式呈现，结合现代装裱与灯光设计，使传统技艺更贴近当代生活审美。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>传统美术</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>国家级非物质文化遗产</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寿山石雕是中国福建省福州市最具代表性的传统雕刻艺术之一，以产自福州北峰寿山乡一带的寿山石为原材料，通过独特的雕刻技艺制作出人物、动物、山水、花鸟、印章等各类艺术品。它历史悠久、技法丰富、风格独特，被誉为“榕城三绝”之一（与脱胎漆器、软木画并列），并于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2006</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日被国务院正式列入第一批国家级非物质文化遗产名录，遗产编号为Ⅶ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>-35</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，类别为“传统美术”。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寿山石雕的历史可追溯至</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>多年前。考古发现表明，最古老的寿山石雕实物出土于南朝墓葬，如</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1954</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年在福州仓山区桃花山福建师范学院工地发现的一件伏卧状石猪，高仅</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>厘米，长</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>6.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>厘米，由寿山老岭石雕刻而成，刀法简练、造型粗犷。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1965</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年在福州北郊二凤山发掘的南朝墓中，还出土了带有“元嘉二十二年”（公元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>445</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年）纪年砖的同类石猪一对，确证寿山石雕至少始于南北朝时期。此后，历经唐宋发展、元明转型，至清代达到鼎盛。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>南宋时期，寿山石矿已大规模开采，《观石录》等文献记载其已被列为贡品。元明之际，文人开始用寿山石刻制印章，因其质地温润如玉、柔而易攻，迅速受到书画家和篆刻家青睐，推动了印钮雕刻艺术的兴起。明代寿山石章成为文人雅士珍藏之物，印钮雕刻在继承古代玉玺、铜印风格基础上不断创新，形成独特风貌。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>清代是寿山石雕的黄金时代。雍正年间，寿山石雕已纳入官府征税范围；乾隆皇帝曾使用一套由整块田黄石雕刻而成、以两根链条连接三枚印章的“宝印”，工艺精湛，堪称国宝。这一时期，寿山石雕不仅用于印章，还广泛制作文具、人物、动物及镶嵌器皿，技法上发展出阴刻、链雕、高浮雕等新形式，并形成两大主要流派：东门派与西门派。东门派以鼓山后屿为中心，风格雄健写实；西门派以洪山一带为主，讲究含蓄雅致。两派在清同治、光绪年间趋于成熟，代表人物如林谦培、潘玉茂及其传人林清卿、郑仁蛟等，对后世影响深远。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寿山石雕的技法极为多样，主要包括圆雕、印钮雕、薄意雕、镂空雕、浅浮雕、高浮雕、链雕、镶嵌雕、篆刻和微雕等。其中，“薄意雕”是寿山石雕独创的一种浅浮雕技法，融合中国画意境，讲究“以刀代笔”，层次虽薄却意境深远。而“相石”被视为创作的核心环节，素有“一相抵九工”之说——即构思设计的重要性远超实际雕刻工时。艺人需根据石料的形状、色泽、纹理甚至裂痕进行巧妙构思，因材施艺、因色取巧，最大限度利用天然色彩与瑕疵，追求“天工合一”的艺术境界。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>寿山石本身色彩丰富，有红、黄、白、黑、灰、紫、绿等十余种颜色，常呈自然交融的斑纹。其中尤以“田黄石”最为珍贵，被誉为“石中之帝”，具有黄皮、红筋、萝卜丝纹三大特征，历史上曾有“一两田黄三两金”之说。寿山石按产地分为三大类：田坑（如田黄）、水坑（如水晶冻、鱼脑冻）、山坑（如高山石、杜陵石、月尾石等），每类下又细分数十个品种，材质特性各异，直接影响雕刻风格与题材选择。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>现代寿山石雕题材广泛，既有传统神话人物（如观音、罗汉、八仙）、瑞兽（如龙、狮、貔貅），也有反映现实生活或重大历史事件的作品，如《长征组雕》《红色闽西》《武夷风光》《海底世界》等。代表性大师包括冯久和（《猪崽满圈》）、郭功森（山水雕）、林亨云（群鱼雕）、林发述（《三仙醉酒》）、王祖光（《荷花观音》）等，他们的作品将写实与写意结合，兼具工艺性与艺术性。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>从工艺流程看，一件寿山石雕至少需经历五道工序：相石（构思设计）、打坯（粗雕定型）、凿坯（细部刻画）、修光（精修表面）、磨光（抛光润泽）。整个过程全凭手工完成，强调手感与经验，尤其在处理巧色和裂纹时，更需匠人极高的审美判断与应变能力。优质作品通常不拼接、不染色，保持石材天然完整性。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>近年来，寿山石雕面临资源枯竭、技艺传承断层等挑战。为加强保护，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>2019</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>月，寿山石雕被列入“国家级非物质文化遗产代表性项目保护单位名单”。福州市晋安区的寿山乡、象园、岳峰镇等地仍是主要传承区域，当地设有寿山石雕艺术馆、博物馆及多个大师工作室。同时，年轻一代艺术家也在尝试跨界融合，如结合当代雕塑语言、数字设计或生活美学，推动传统技艺走向现代生活。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寿山石雕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《乾隆田黄三联章》是寿山石雕中最著名的国宝级文物。这组印章由整块田黄石雕刻而成，包含三方印玺——“乾隆宸翰”“惟精惟一”和“乐天”，以两条精细的活动链条相连，链环可自由转动，工艺极为复杂。此作完成于清代乾隆年间，由宫廷匠人精心雕琢，现藏于北京故宫博物院。它不仅体现了清代寿山石雕的巅峰技艺，也因材质为稀世田黄石而被视为“石帝”中的极品，常作为中国玉雕与石雕艺术的象征性展品。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《猪崽满圈》是现代寿山石雕的里程碑式作品，由国家级非遗传承人、中国工艺美术大师冯久和于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>1970</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年代创作。作品以高山石为材，雕刻出母猪带领十余只形态各异的小猪在圈中嬉戏的场景，生动活泼、充满生活气息。该作突破了传统寿山石雕偏重宗教或文人题材的局限，将农村生活引入高雅艺术，曾获全国工艺美术百花奖，并被中国工艺美术馆收藏，成为现实主义题材寿山石雕的典范。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《海底世界》是郭功森（中国工艺美术大师）的代表作之一，采用大型高山石，运用高浮雕与镂空雕技法，刻画鱼群穿梭、海藻摇曳、珊瑚林立的海洋生态，层次丰富、动感十足。作品融合山水构图与动物雕刻，展现了寿山石雕在表现宏大场景上的能力，也体现了“因色取巧、依形就势”的创作理念。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《群鱼》系列由林亨云（中国工艺美术大师）创作，以寿山石中的黑、灰、白色石材巧妙表现鲤鱼、鳜鱼等不同鱼类的质感与动态。他尤其擅长利用石材天然纹理模拟鱼鳞光泽，鱼眼炯炯有神，鱼尾似在摆动，被誉为“鱼王”。其作品《寒冬一霸》（北极熊与鱼）更将动物雕刻推向写实与情感表达的新高度。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《荷花观音》出自王祖光之手，以洁白芙蓉石雕刻观音立于荷叶之上，衣袂飘逸、面容慈祥，背景荷叶翻卷自然，整体清雅脱俗。该作融合佛教造像传统与寿山石温润特质，体现“相石取神”的美学追求，是人物雕刻的经典。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>《三仙醉酒》由林发述创作，刻画铁拐李、汉钟离、吕洞宾三位神仙醉态可掬的形象，神情夸张却不失神韵，刀法洗练而富戏剧性，充分展现西门派“重神韵、尚意境”的风格。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>此外，还有如周宝庭的古兽印钮、林清卿的薄意雕《赤壁赋》《米癫拜石》等，也是极具代表性的作品。林清卿尤以“薄意”闻名，他将中国画的笔墨意境转化为浅层雕刻，线条如行云流水，被誉为“西门清卿，薄意第一”。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111133"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当代作品中，《武夷春色》《闽山闽水》《红色闽西》等大型主题雕刻，也常被选送人民大会堂或作为国家礼品，体现寿山石雕在新时代的叙事能力与文化担当</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +1310,41 @@
       <color rgb="FF111133"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111133"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111133"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111133"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111133"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF111133"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -206,7 +1390,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -214,6 +1398,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -488,6 +1684,8 @@
   <cols>
     <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="224.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="69.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -510,104 +1708,104 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="300" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:6" ht="375" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="409.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="360" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="5" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="300" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="300" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="345" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
